--- a/湖北农信新信贷数据库设计文档/新信贷_数据库设计_评级管理v1.0.1.xlsx
+++ b/湖北农信新信贷数据库设计文档/新信贷_数据库设计_评级管理v1.0.1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12540" activeTab="4"/>
+    <workbookView windowWidth="28800" windowHeight="12540" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="修订记录" sheetId="1" r:id="rId1"/>
@@ -17,12 +17,12 @@
     <sheet name="综合评价信息表" sheetId="8" r:id="rId8"/>
     <sheet name="结果信息表" sheetId="9" r:id="rId9"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="144525" iterate="1" iterateCount="100" iterateDelta="0.001"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="368">
   <si>
     <t>序号</t>
   </si>
@@ -351,6 +351,9 @@
     <t>变更日期</t>
   </si>
   <si>
+    <t>字段是否迁有值</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -958,9 +961,6 @@
   </si>
   <si>
     <t>SCR_CRD_DETLD</t>
-  </si>
-  <si>
-    <t>VARCHAR(8000)</t>
   </si>
   <si>
     <t>评分卡详情</t>
@@ -3430,7 +3430,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N34"/>
+  <dimension ref="A1:O34"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -3438,9 +3438,10 @@
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:13">
+    <row r="1" ht="18" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3480,10 +3481,13 @@
       <c r="M1" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:14">
+      <c r="O1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>63</v>
@@ -3492,16 +3496,16 @@
         <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -3512,12 +3516,15 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:13">
+        <v>114</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>63</v>
@@ -3529,13 +3536,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -3543,10 +3550,13 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:13">
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>63</v>
@@ -3555,16 +3565,16 @@
         <v>64</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -3572,10 +3582,13 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:13">
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>63</v>
@@ -3584,16 +3597,16 @@
         <v>64</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -3601,10 +3614,13 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:13">
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>63</v>
@@ -3613,29 +3629,32 @@
         <v>64</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:13">
+      <c r="O6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>63</v>
@@ -3644,16 +3663,16 @@
         <v>64</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -3661,10 +3680,13 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:13">
+      <c r="O7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>63</v>
@@ -3673,16 +3695,16 @@
         <v>64</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -3690,10 +3712,13 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:13">
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>63</v>
@@ -3702,16 +3727,16 @@
         <v>64</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -3719,10 +3744,13 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:13">
+      <c r="O9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>63</v>
@@ -3731,29 +3759,32 @@
         <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:13">
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>63</v>
@@ -3762,16 +3793,16 @@
         <v>64</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -3779,10 +3810,13 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:13">
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>63</v>
@@ -3791,29 +3825,32 @@
         <v>64</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:13">
+      <c r="O12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>63</v>
@@ -3822,29 +3859,32 @@
         <v>64</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:13">
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>63</v>
@@ -3853,29 +3893,32 @@
         <v>64</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:13">
+      <c r="O14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>63</v>
@@ -3884,29 +3927,32 @@
         <v>64</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:13">
+      <c r="O15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>63</v>
@@ -3915,16 +3961,16 @@
         <v>64</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -3932,10 +3978,13 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:13">
+      <c r="O16" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>63</v>
@@ -3944,29 +3993,32 @@
         <v>64</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:13">
+      <c r="O17" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>63</v>
@@ -3975,16 +4027,16 @@
         <v>64</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -3992,10 +4044,13 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:13">
+      <c r="O18" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>63</v>
@@ -4004,16 +4059,16 @@
         <v>64</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
@@ -4021,10 +4076,13 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:13">
+      <c r="O19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>63</v>
@@ -4033,16 +4091,16 @@
         <v>64</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -4050,10 +4108,13 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:13">
+      <c r="O20" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>63</v>
@@ -4062,16 +4123,16 @@
         <v>64</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
@@ -4079,10 +4140,13 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:13">
+      <c r="O21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>63</v>
@@ -4091,16 +4155,16 @@
         <v>64</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -4108,10 +4172,13 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:13">
+      <c r="O22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>63</v>
@@ -4120,16 +4187,16 @@
         <v>64</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -4137,10 +4204,13 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:13">
+      <c r="O23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>63</v>
@@ -4149,16 +4219,16 @@
         <v>64</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
@@ -4166,10 +4236,13 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:13">
+      <c r="O24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>63</v>
@@ -4178,16 +4251,16 @@
         <v>64</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -4195,10 +4268,13 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:13">
+      <c r="O25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>63</v>
@@ -4207,16 +4283,16 @@
         <v>64</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
@@ -4224,10 +4300,13 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:13">
+      <c r="O26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>63</v>
@@ -4236,16 +4315,16 @@
         <v>64</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
@@ -4253,10 +4332,13 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:13">
+      <c r="O27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>63</v>
@@ -4265,16 +4347,16 @@
         <v>64</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
@@ -4282,10 +4364,13 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:13">
+      <c r="O28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:15">
       <c r="A29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>63</v>
@@ -4294,29 +4379,32 @@
         <v>64</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="2"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:13">
+      <c r="O29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>63</v>
@@ -4325,16 +4413,16 @@
         <v>64</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
@@ -4342,10 +4430,13 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="2"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:13">
+      <c r="O30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:15">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>63</v>
@@ -4354,16 +4445,16 @@
         <v>64</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
@@ -4371,10 +4462,13 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="2"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:13">
+      <c r="O31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>63</v>
@@ -4383,16 +4477,16 @@
         <v>64</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
@@ -4400,10 +4494,13 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:13">
+      <c r="O32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:15">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>63</v>
@@ -4412,16 +4509,16 @@
         <v>64</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
@@ -4429,6 +4526,9 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="2"/>
+      <c r="O33" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="34" spans="9:9">
       <c r="I34" s="4"/>
@@ -4445,7 +4545,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N55"/>
+  <dimension ref="A1:O55"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4453,9 +4553,10 @@
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:13">
+    <row r="1" ht="18" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4495,10 +4596,13 @@
       <c r="M1" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:14">
+      <c r="O1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>70</v>
@@ -4507,16 +4611,16 @@
         <v>71</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -4527,12 +4631,15 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:13">
+        <v>114</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>70</v>
@@ -4544,13 +4651,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -4558,10 +4665,13 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:13">
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>70</v>
@@ -4570,16 +4680,16 @@
         <v>71</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -4587,10 +4697,13 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:13">
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>70</v>
@@ -4599,16 +4712,16 @@
         <v>71</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -4616,10 +4729,13 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:13">
+      <c r="O5" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>70</v>
@@ -4628,16 +4744,16 @@
         <v>71</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
@@ -4645,10 +4761,13 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:13">
+      <c r="O6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>70</v>
@@ -4657,29 +4776,32 @@
         <v>71</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:13">
+      <c r="O7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>70</v>
@@ -4688,29 +4810,32 @@
         <v>71</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J8" s="3"/>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:13">
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>70</v>
@@ -4719,16 +4844,16 @@
         <v>71</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -4736,10 +4861,13 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:13">
+      <c r="O9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>70</v>
@@ -4748,16 +4876,16 @@
         <v>71</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -4765,10 +4893,13 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:13">
+      <c r="O10" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>70</v>
@@ -4777,16 +4908,16 @@
         <v>71</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -4794,10 +4925,13 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:13">
+      <c r="O11" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>70</v>
@@ -4806,16 +4940,16 @@
         <v>71</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -4823,10 +4957,13 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:13">
+      <c r="O12" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>70</v>
@@ -4835,16 +4972,16 @@
         <v>71</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -4852,10 +4989,13 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:13">
+      <c r="O13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>70</v>
@@ -4864,16 +5004,16 @@
         <v>71</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -4881,10 +5021,13 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:13">
+      <c r="O14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>70</v>
@@ -4893,16 +5036,16 @@
         <v>71</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -4910,10 +5053,13 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:13">
+      <c r="O15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>70</v>
@@ -4922,16 +5068,16 @@
         <v>71</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -4939,10 +5085,13 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:13">
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>70</v>
@@ -4951,16 +5100,16 @@
         <v>71</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
@@ -4968,10 +5117,13 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:13">
+      <c r="O17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>70</v>
@@ -4980,16 +5132,16 @@
         <v>71</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -4997,10 +5149,13 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:13">
+      <c r="O18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>70</v>
@@ -5009,29 +5164,32 @@
         <v>71</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:13">
+      <c r="O19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>70</v>
@@ -5040,16 +5198,16 @@
         <v>71</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -5057,10 +5215,13 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:13">
+      <c r="O20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>70</v>
@@ -5069,16 +5230,16 @@
         <v>71</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
@@ -5086,10 +5247,13 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:13">
+      <c r="O21" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>70</v>
@@ -5098,16 +5262,16 @@
         <v>71</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -5115,10 +5279,13 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:13">
+      <c r="O22" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>70</v>
@@ -5127,16 +5294,16 @@
         <v>71</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -5144,10 +5311,13 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:13">
+      <c r="O23" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>70</v>
@@ -5156,16 +5326,16 @@
         <v>71</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
@@ -5173,10 +5343,13 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:13">
+      <c r="O24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>70</v>
@@ -5185,16 +5358,16 @@
         <v>71</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -5202,10 +5375,13 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:13">
+      <c r="O25" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>70</v>
@@ -5214,16 +5390,16 @@
         <v>71</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
@@ -5231,10 +5407,13 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:13">
+      <c r="O26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>70</v>
@@ -5243,16 +5422,16 @@
         <v>71</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
@@ -5260,10 +5439,13 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:13">
+      <c r="O27" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>70</v>
@@ -5272,16 +5454,16 @@
         <v>71</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
@@ -5289,10 +5471,13 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:13">
+      <c r="O28" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:15">
       <c r="A29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>70</v>
@@ -5301,16 +5486,16 @@
         <v>71</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
@@ -5318,10 +5503,13 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="2"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:13">
+      <c r="O29" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>70</v>
@@ -5330,16 +5518,16 @@
         <v>71</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
@@ -5347,10 +5535,13 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="2"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:13">
+      <c r="O30" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:15">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>70</v>
@@ -5359,16 +5550,16 @@
         <v>71</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
@@ -5376,10 +5567,13 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="2"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:13">
+      <c r="O31" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>70</v>
@@ -5388,16 +5582,16 @@
         <v>71</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="4"/>
@@ -5405,10 +5599,13 @@
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:13">
+      <c r="O32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:15">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>70</v>
@@ -5417,16 +5614,16 @@
         <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
@@ -5434,10 +5631,13 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="2"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:13">
+      <c r="O33" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:15">
       <c r="A34" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>70</v>
@@ -5446,16 +5646,16 @@
         <v>71</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
@@ -5463,10 +5663,13 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="2"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:13">
+      <c r="O34" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:15">
       <c r="A35" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>70</v>
@@ -5475,16 +5678,16 @@
         <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
@@ -5492,10 +5695,13 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="2"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:13">
+      <c r="O35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>70</v>
@@ -5504,16 +5710,16 @@
         <v>71</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
@@ -5521,10 +5727,13 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="2"/>
-    </row>
-    <row r="37" ht="18" customHeight="1" spans="1:13">
+      <c r="O36" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" ht="18" customHeight="1" spans="1:15">
       <c r="A37" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>70</v>
@@ -5533,16 +5742,16 @@
         <v>71</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H37" s="3"/>
       <c r="I37" s="4"/>
@@ -5550,10 +5759,13 @@
       <c r="K37" s="3"/>
       <c r="L37" s="3"/>
       <c r="M37" s="2"/>
-    </row>
-    <row r="38" ht="18" customHeight="1" spans="1:13">
+      <c r="O37" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="38" ht="18" customHeight="1" spans="1:15">
       <c r="A38" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>70</v>
@@ -5562,16 +5774,16 @@
         <v>71</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H38" s="3"/>
       <c r="I38" s="4"/>
@@ -5579,10 +5791,13 @@
       <c r="K38" s="3"/>
       <c r="L38" s="3"/>
       <c r="M38" s="2"/>
-    </row>
-    <row r="39" ht="18" customHeight="1" spans="1:13">
+      <c r="O38" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" ht="18" customHeight="1" spans="1:15">
       <c r="A39" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>70</v>
@@ -5591,16 +5806,16 @@
         <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="F39" s="2" t="s">
         <v>313</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H39" s="3"/>
       <c r="I39" s="4"/>
@@ -5608,8 +5823,11 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="2"/>
-    </row>
-    <row r="40" ht="18" customHeight="1" spans="1:13">
+      <c r="O39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" ht="18" customHeight="1" spans="1:15">
       <c r="A40" s="2" t="s">
         <v>314</v>
       </c>
@@ -5620,16 +5838,16 @@
         <v>71</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H40" s="3"/>
       <c r="I40" s="4"/>
@@ -5637,8 +5855,11 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="2"/>
-    </row>
-    <row r="41" ht="18" customHeight="1" spans="1:13">
+      <c r="O40" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:15">
       <c r="A41" s="2" t="s">
         <v>315</v>
       </c>
@@ -5649,16 +5870,16 @@
         <v>71</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="4"/>
@@ -5666,8 +5887,11 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
       <c r="M41" s="2"/>
-    </row>
-    <row r="42" ht="18" customHeight="1" spans="1:13">
+      <c r="O41" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" ht="18" customHeight="1" spans="1:15">
       <c r="A42" s="2" t="s">
         <v>316</v>
       </c>
@@ -5678,16 +5902,16 @@
         <v>71</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="4"/>
@@ -5695,8 +5919,11 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
       <c r="M42" s="2"/>
-    </row>
-    <row r="43" ht="18" customHeight="1" spans="1:13">
+      <c r="O42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" ht="18" customHeight="1" spans="1:15">
       <c r="A43" s="2" t="s">
         <v>317</v>
       </c>
@@ -5707,16 +5934,16 @@
         <v>71</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="4"/>
@@ -5724,8 +5951,11 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
       <c r="M43" s="2"/>
-    </row>
-    <row r="44" ht="18" customHeight="1" spans="1:13">
+      <c r="O43" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="44" ht="18" customHeight="1" spans="1:15">
       <c r="A44" s="2" t="s">
         <v>318</v>
       </c>
@@ -5736,16 +5966,16 @@
         <v>71</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="4"/>
@@ -5753,8 +5983,11 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
       <c r="M44" s="2"/>
-    </row>
-    <row r="45" ht="18" customHeight="1" spans="1:13">
+      <c r="O44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" ht="18" customHeight="1" spans="1:15">
       <c r="A45" s="2" t="s">
         <v>319</v>
       </c>
@@ -5765,16 +5998,16 @@
         <v>71</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="4"/>
@@ -5782,8 +6015,11 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
       <c r="M45" s="2"/>
-    </row>
-    <row r="46" ht="18" customHeight="1" spans="1:13">
+      <c r="O45" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" ht="18" customHeight="1" spans="1:15">
       <c r="A46" s="2" t="s">
         <v>320</v>
       </c>
@@ -5794,16 +6030,16 @@
         <v>71</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H46" s="3"/>
       <c r="I46" s="4"/>
@@ -5811,8 +6047,11 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
       <c r="M46" s="2"/>
-    </row>
-    <row r="47" ht="18" customHeight="1" spans="1:13">
+      <c r="O46" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="47" ht="18" customHeight="1" spans="1:15">
       <c r="A47" s="2" t="s">
         <v>321</v>
       </c>
@@ -5823,16 +6062,16 @@
         <v>71</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H47" s="3"/>
       <c r="I47" s="4"/>
@@ -5840,8 +6079,11 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
       <c r="M47" s="2"/>
-    </row>
-    <row r="48" ht="18" customHeight="1" spans="1:13">
+      <c r="O47" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="48" ht="18" customHeight="1" spans="1:15">
       <c r="A48" s="2" t="s">
         <v>322</v>
       </c>
@@ -5852,16 +6094,16 @@
         <v>71</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H48" s="3"/>
       <c r="I48" s="4"/>
@@ -5869,8 +6111,11 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
       <c r="M48" s="2"/>
-    </row>
-    <row r="49" ht="18" customHeight="1" spans="1:13">
+      <c r="O48" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="49" ht="18" customHeight="1" spans="1:15">
       <c r="A49" s="2" t="s">
         <v>323</v>
       </c>
@@ -5881,16 +6126,16 @@
         <v>71</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H49" s="3"/>
       <c r="I49" s="4"/>
@@ -5898,8 +6143,11 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
       <c r="M49" s="2"/>
-    </row>
-    <row r="50" ht="18" customHeight="1" spans="1:13">
+      <c r="O49" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:15">
       <c r="A50" s="2" t="s">
         <v>324</v>
       </c>
@@ -5910,27 +6158,30 @@
         <v>71</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H50" s="3"/>
       <c r="I50" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
       <c r="M50" s="2"/>
-    </row>
-    <row r="51" ht="18" customHeight="1" spans="1:13">
+      <c r="O50" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="51" ht="18" customHeight="1" spans="1:15">
       <c r="A51" s="2" t="s">
         <v>325</v>
       </c>
@@ -5941,16 +6192,16 @@
         <v>71</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H51" s="3"/>
       <c r="I51" s="4"/>
@@ -5958,8 +6209,11 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
       <c r="M51" s="2"/>
-    </row>
-    <row r="52" ht="18" customHeight="1" spans="1:13">
+      <c r="O51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" ht="18" customHeight="1" spans="1:15">
       <c r="A52" s="2" t="s">
         <v>326</v>
       </c>
@@ -5970,16 +6224,16 @@
         <v>71</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H52" s="3"/>
       <c r="I52" s="4"/>
@@ -5987,8 +6241,11 @@
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
       <c r="M52" s="2"/>
-    </row>
-    <row r="53" ht="18" customHeight="1" spans="1:13">
+      <c r="O52" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1" spans="1:15">
       <c r="A53" s="2" t="s">
         <v>327</v>
       </c>
@@ -5999,16 +6256,16 @@
         <v>71</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H53" s="3"/>
       <c r="I53" s="4"/>
@@ -6016,8 +6273,11 @@
       <c r="K53" s="3"/>
       <c r="L53" s="3"/>
       <c r="M53" s="2"/>
-    </row>
-    <row r="54" ht="18" customHeight="1" spans="1:13">
+      <c r="O53" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" ht="18" customHeight="1" spans="1:15">
       <c r="A54" s="2" t="s">
         <v>328</v>
       </c>
@@ -6028,16 +6288,16 @@
         <v>71</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H54" s="3"/>
       <c r="I54" s="4"/>
@@ -6045,6 +6305,9 @@
       <c r="K54" s="3"/>
       <c r="L54" s="3"/>
       <c r="M54" s="2"/>
+      <c r="O54" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="55" spans="9:9">
       <c r="I55" s="4"/>
@@ -6114,7 +6377,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>72</v>
@@ -6123,16 +6386,16 @@
         <v>73</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -6143,12 +6406,12 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>72</v>
@@ -6160,13 +6423,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -6177,7 +6440,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>72</v>
@@ -6189,13 +6452,13 @@
         <v>329</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -6206,7 +6469,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>72</v>
@@ -6218,13 +6481,13 @@
         <v>330</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>331</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -6235,7 +6498,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>72</v>
@@ -6247,13 +6510,13 @@
         <v>332</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>333</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
@@ -6264,7 +6527,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>72</v>
@@ -6276,13 +6539,13 @@
         <v>334</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>335</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -6293,7 +6556,7 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>72</v>
@@ -6302,16 +6565,16 @@
         <v>73</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -6322,7 +6585,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>72</v>
@@ -6331,16 +6594,16 @@
         <v>73</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -6351,7 +6614,7 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>72</v>
@@ -6360,16 +6623,16 @@
         <v>73</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -6380,7 +6643,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>72</v>
@@ -6389,16 +6652,16 @@
         <v>73</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -6409,7 +6672,7 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>72</v>
@@ -6418,16 +6681,16 @@
         <v>73</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -6438,7 +6701,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>72</v>
@@ -6447,16 +6710,16 @@
         <v>73</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -6467,7 +6730,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>72</v>
@@ -6476,16 +6739,16 @@
         <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -6496,7 +6759,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>72</v>
@@ -6505,16 +6768,16 @@
         <v>73</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -6525,7 +6788,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>72</v>
@@ -6534,16 +6797,16 @@
         <v>73</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -6554,7 +6817,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>72</v>
@@ -6563,16 +6826,16 @@
         <v>73</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
@@ -6583,7 +6846,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>72</v>
@@ -6592,16 +6855,16 @@
         <v>73</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -6612,7 +6875,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>72</v>
@@ -6621,16 +6884,16 @@
         <v>73</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
@@ -6641,7 +6904,7 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>72</v>
@@ -6650,16 +6913,16 @@
         <v>73</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -6670,7 +6933,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>72</v>
@@ -6679,20 +6942,20 @@
         <v>73</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -6701,7 +6964,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:13">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>72</v>
@@ -6710,16 +6973,16 @@
         <v>73</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -6730,7 +6993,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>72</v>
@@ -6739,16 +7002,16 @@
         <v>73</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -6759,7 +7022,7 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>72</v>
@@ -6768,16 +7031,16 @@
         <v>73</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
@@ -6788,7 +7051,7 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:13">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>72</v>
@@ -6797,16 +7060,16 @@
         <v>73</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -6883,7 +7146,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>74</v>
@@ -6892,16 +7155,16 @@
         <v>75</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -6912,12 +7175,12 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>74</v>
@@ -6929,13 +7192,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -6946,7 +7209,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>74</v>
@@ -6958,13 +7221,13 @@
         <v>329</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>0</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -6975,7 +7238,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>74</v>
@@ -6987,13 +7250,13 @@
         <v>330</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>331</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -7004,7 +7267,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>74</v>
@@ -7016,13 +7279,13 @@
         <v>332</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>333</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
@@ -7033,7 +7296,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>74</v>
@@ -7042,16 +7305,16 @@
         <v>75</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -7062,7 +7325,7 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>74</v>
@@ -7071,16 +7334,16 @@
         <v>75</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -7091,7 +7354,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>74</v>
@@ -7100,16 +7363,16 @@
         <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -7120,7 +7383,7 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>74</v>
@@ -7129,16 +7392,16 @@
         <v>75</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -7149,7 +7412,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>74</v>
@@ -7158,16 +7421,16 @@
         <v>75</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -7178,7 +7441,7 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>74</v>
@@ -7187,16 +7450,16 @@
         <v>75</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -7207,7 +7470,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>74</v>
@@ -7216,16 +7479,16 @@
         <v>75</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -7236,7 +7499,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>74</v>
@@ -7245,16 +7508,16 @@
         <v>75</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -7265,7 +7528,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>74</v>
@@ -7274,16 +7537,16 @@
         <v>75</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -7294,7 +7557,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>74</v>
@@ -7303,16 +7566,16 @@
         <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -7323,7 +7586,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>74</v>
@@ -7332,16 +7595,16 @@
         <v>75</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
@@ -7352,7 +7615,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>74</v>
@@ -7361,16 +7624,16 @@
         <v>75</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -7381,7 +7644,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>74</v>
@@ -7390,20 +7653,20 @@
         <v>75</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -7412,7 +7675,7 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>74</v>
@@ -7421,16 +7684,16 @@
         <v>75</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -7441,7 +7704,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>74</v>
@@ -7450,16 +7713,16 @@
         <v>75</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
@@ -7470,7 +7733,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:13">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>74</v>
@@ -7479,16 +7742,16 @@
         <v>75</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -7499,7 +7762,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>74</v>
@@ -7508,16 +7771,16 @@
         <v>75</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -7594,7 +7857,7 @@
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>76</v>
@@ -7603,16 +7866,16 @@
         <v>77</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -7623,12 +7886,12 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:13">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>76</v>
@@ -7640,13 +7903,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -7657,7 +7920,7 @@
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>76</v>
@@ -7669,13 +7932,13 @@
         <v>336</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>337</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -7686,7 +7949,7 @@
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>76</v>
@@ -7704,7 +7967,7 @@
         <v>340</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -7715,7 +7978,7 @@
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>76</v>
@@ -7733,7 +7996,7 @@
         <v>343</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4"/>
@@ -7744,7 +8007,7 @@
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:13">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>76</v>
@@ -7756,13 +8019,13 @@
         <v>344</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>345</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -7773,7 +8036,7 @@
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>76</v>
@@ -7785,13 +8048,13 @@
         <v>346</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>347</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -7802,7 +8065,7 @@
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>76</v>
@@ -7814,13 +8077,13 @@
         <v>348</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>349</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -7831,7 +8094,7 @@
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:13">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>76</v>
@@ -7843,13 +8106,13 @@
         <v>350</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>351</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -7860,7 +8123,7 @@
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:13">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>76</v>
@@ -7869,16 +8132,16 @@
         <v>77</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -7889,7 +8152,7 @@
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:13">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>76</v>
@@ -7898,16 +8161,16 @@
         <v>77</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -7918,7 +8181,7 @@
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:13">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>76</v>
@@ -7927,16 +8190,16 @@
         <v>77</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -7947,7 +8210,7 @@
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>76</v>
@@ -7956,16 +8219,16 @@
         <v>77</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -7976,7 +8239,7 @@
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>76</v>
@@ -7985,16 +8248,16 @@
         <v>77</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -8005,7 +8268,7 @@
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:13">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>76</v>
@@ -8014,16 +8277,16 @@
         <v>77</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -8034,7 +8297,7 @@
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:13">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>76</v>
@@ -8043,16 +8306,16 @@
         <v>77</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
@@ -8063,7 +8326,7 @@
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:13">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>76</v>
@@ -8072,16 +8335,16 @@
         <v>77</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4"/>
@@ -8092,7 +8355,7 @@
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:13">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>76</v>
@@ -8101,16 +8364,16 @@
         <v>77</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
@@ -8121,7 +8384,7 @@
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:13">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>76</v>
@@ -8130,16 +8393,16 @@
         <v>77</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -8150,7 +8413,7 @@
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:13">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>76</v>
@@ -8159,20 +8422,20 @@
         <v>77</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
@@ -8181,7 +8444,7 @@
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:13">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>76</v>
@@ -8190,16 +8453,16 @@
         <v>77</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -8210,7 +8473,7 @@
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:13">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>76</v>
@@ -8219,16 +8482,16 @@
         <v>77</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -8239,7 +8502,7 @@
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:13">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>76</v>
@@ -8248,16 +8511,16 @@
         <v>77</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
@@ -8268,7 +8531,7 @@
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:13">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>76</v>
@@ -8277,16 +8540,16 @@
         <v>77</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -8310,7 +8573,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:O37"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -8318,9 +8581,10 @@
     <col min="7" max="7" width="15" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
     <col min="13" max="13" width="20" customWidth="1"/>
+    <col min="15" max="15" width="15" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1" spans="1:13">
+    <row r="1" ht="18" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8360,10 +8624,13 @@
       <c r="M1" s="1" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="2" ht="18" customHeight="1" spans="1:14">
+      <c r="O1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1" spans="1:15">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>78</v>
@@ -8372,16 +8639,16 @@
         <v>79</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>65</v>
@@ -8392,12 +8659,15 @@
       <c r="L2" s="3"/>
       <c r="M2" s="2"/>
       <c r="N2" s="5" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:13">
+        <v>114</v>
+      </c>
+      <c r="O2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:15">
       <c r="A3" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>78</v>
@@ -8409,13 +8679,13 @@
         <v>66</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="4"/>
@@ -8423,10 +8693,13 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="2"/>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:13">
+      <c r="O3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:15">
       <c r="A4" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
@@ -8435,16 +8708,16 @@
         <v>79</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="4"/>
@@ -8452,10 +8725,13 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="2"/>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:13">
+      <c r="O4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>78</v>
@@ -8464,16 +8740,16 @@
         <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="4"/>
@@ -8481,10 +8757,13 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
       <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="18" customHeight="1" spans="1:13">
+      <c r="O5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:15">
       <c r="A6" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>78</v>
@@ -8493,29 +8772,32 @@
         <v>79</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J6" s="3"/>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
       <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="18" customHeight="1" spans="1:13">
+      <c r="O6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:15">
       <c r="A7" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>78</v>
@@ -8527,13 +8809,13 @@
         <v>352</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>353</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="4"/>
@@ -8541,10 +8823,13 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
       <c r="M7" s="2"/>
-    </row>
-    <row r="8" ht="18" customHeight="1" spans="1:13">
+      <c r="O7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:15">
       <c r="A8" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>78</v>
@@ -8556,13 +8841,13 @@
         <v>354</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>355</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="4"/>
@@ -8570,10 +8855,13 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
       <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:13">
+      <c r="O8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:15">
       <c r="A9" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>78</v>
@@ -8585,13 +8873,13 @@
         <v>356</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>357</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="4"/>
@@ -8599,10 +8887,13 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
       <c r="M9" s="2"/>
-    </row>
-    <row r="10" ht="18" customHeight="1" spans="1:13">
+      <c r="O9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:15">
       <c r="A10" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>78</v>
@@ -8614,13 +8905,13 @@
         <v>358</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>359</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="4"/>
@@ -8628,10 +8919,13 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
       <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="18" customHeight="1" spans="1:13">
+      <c r="O10" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:15">
       <c r="A11" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>78</v>
@@ -8643,13 +8937,13 @@
         <v>360</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>361</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="4"/>
@@ -8657,10 +8951,13 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="18" customHeight="1" spans="1:13">
+      <c r="O11" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:15">
       <c r="A12" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>78</v>
@@ -8672,13 +8969,13 @@
         <v>362</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>363</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="4"/>
@@ -8686,10 +8983,13 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
       <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="18" customHeight="1" spans="1:13">
+      <c r="O12" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:15">
       <c r="A13" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>78</v>
@@ -8701,13 +9001,13 @@
         <v>364</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>365</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="4"/>
@@ -8715,10 +9015,13 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
       <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="18" customHeight="1" spans="1:13">
+      <c r="O13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:15">
       <c r="A14" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>78</v>
@@ -8730,13 +9033,13 @@
         <v>366</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>367</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="4"/>
@@ -8744,10 +9047,13 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
       <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="18" customHeight="1" spans="1:13">
+      <c r="O14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:15">
       <c r="A15" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>78</v>
@@ -8756,16 +9062,16 @@
         <v>79</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="4"/>
@@ -8773,10 +9079,13 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
       <c r="M15" s="2"/>
-    </row>
-    <row r="16" ht="18" customHeight="1" spans="1:13">
+      <c r="O15" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:15">
       <c r="A16" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>78</v>
@@ -8785,16 +9094,16 @@
         <v>79</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="4"/>
@@ -8802,10 +9111,13 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="18" customHeight="1" spans="1:13">
+      <c r="O16" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:15">
       <c r="A17" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>78</v>
@@ -8814,16 +9126,16 @@
         <v>79</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="4"/>
@@ -8831,10 +9143,13 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
       <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="18" customHeight="1" spans="1:13">
+      <c r="O17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1" spans="1:15">
       <c r="A18" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>78</v>
@@ -8843,29 +9158,32 @@
         <v>79</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="4" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
       <c r="M18" s="2"/>
-    </row>
-    <row r="19" ht="18" customHeight="1" spans="1:13">
+      <c r="O18" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1" spans="1:15">
       <c r="A19" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>78</v>
@@ -8874,16 +9192,16 @@
         <v>79</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="4"/>
@@ -8891,10 +9209,13 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="2"/>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:13">
+      <c r="O19" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1" spans="1:15">
       <c r="A20" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>78</v>
@@ -8903,16 +9224,16 @@
         <v>79</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="4"/>
@@ -8920,10 +9241,13 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
       <c r="M20" s="2"/>
-    </row>
-    <row r="21" ht="18" customHeight="1" spans="1:13">
+      <c r="O20" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" ht="18" customHeight="1" spans="1:15">
       <c r="A21" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>78</v>
@@ -8932,16 +9256,16 @@
         <v>79</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="4"/>
@@ -8949,10 +9273,13 @@
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
       <c r="M21" s="2"/>
-    </row>
-    <row r="22" ht="18" customHeight="1" spans="1:13">
+      <c r="O21" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1" spans="1:15">
       <c r="A22" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>78</v>
@@ -8961,16 +9288,16 @@
         <v>79</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="4"/>
@@ -8978,10 +9305,13 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
       <c r="M22" s="2"/>
-    </row>
-    <row r="23" ht="18" customHeight="1" spans="1:13">
+      <c r="O22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:15">
       <c r="A23" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>78</v>
@@ -8990,16 +9320,16 @@
         <v>79</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="4"/>
@@ -9007,10 +9337,13 @@
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
       <c r="M23" s="2"/>
-    </row>
-    <row r="24" ht="18" customHeight="1" spans="1:13">
+      <c r="O23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1" spans="1:15">
       <c r="A24" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>78</v>
@@ -9019,16 +9352,16 @@
         <v>79</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="4"/>
@@ -9036,10 +9369,13 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
       <c r="M24" s="2"/>
-    </row>
-    <row r="25" ht="18" customHeight="1" spans="1:13">
+      <c r="O24" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1" spans="1:15">
       <c r="A25" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>78</v>
@@ -9048,16 +9384,16 @@
         <v>79</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="4"/>
@@ -9065,10 +9401,13 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
       <c r="M25" s="2"/>
-    </row>
-    <row r="26" ht="18" customHeight="1" spans="1:13">
+      <c r="O25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1" spans="1:15">
       <c r="A26" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>78</v>
@@ -9077,16 +9416,16 @@
         <v>79</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="4"/>
@@ -9094,10 +9433,13 @@
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
       <c r="M26" s="2"/>
-    </row>
-    <row r="27" ht="18" customHeight="1" spans="1:13">
+      <c r="O26" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1" spans="1:15">
       <c r="A27" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>78</v>
@@ -9106,16 +9448,16 @@
         <v>79</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="4"/>
@@ -9123,10 +9465,13 @@
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
       <c r="M27" s="2"/>
-    </row>
-    <row r="28" ht="18" customHeight="1" spans="1:13">
+      <c r="O27" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" ht="18" customHeight="1" spans="1:15">
       <c r="A28" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>78</v>
@@ -9135,16 +9480,16 @@
         <v>79</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="4"/>
@@ -9152,10 +9497,13 @@
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
       <c r="M28" s="2"/>
-    </row>
-    <row r="29" ht="18" customHeight="1" spans="1:13">
+      <c r="O28" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1" spans="1:15">
       <c r="A29" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>78</v>
@@ -9164,16 +9512,16 @@
         <v>79</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="4"/>
@@ -9181,10 +9529,13 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
       <c r="M29" s="2"/>
-    </row>
-    <row r="30" ht="18" customHeight="1" spans="1:13">
+      <c r="O29" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1" spans="1:15">
       <c r="A30" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>78</v>
@@ -9193,16 +9544,16 @@
         <v>79</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="4"/>
@@ -9210,10 +9561,13 @@
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
       <c r="M30" s="2"/>
-    </row>
-    <row r="31" ht="18" customHeight="1" spans="1:13">
+      <c r="O30" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1" spans="1:15">
       <c r="A31" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>78</v>
@@ -9222,16 +9576,16 @@
         <v>79</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="4"/>
@@ -9239,10 +9593,13 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="2"/>
-    </row>
-    <row r="32" ht="18" customHeight="1" spans="1:13">
+      <c r="O31" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:15">
       <c r="A32" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>78</v>
@@ -9251,29 +9608,32 @@
         <v>79</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
       <c r="M32" s="2"/>
-    </row>
-    <row r="33" ht="18" customHeight="1" spans="1:13">
+      <c r="O32" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="33" ht="18" customHeight="1" spans="1:15">
       <c r="A33" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>78</v>
@@ -9282,16 +9642,16 @@
         <v>79</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="4"/>
@@ -9299,10 +9659,13 @@
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
       <c r="M33" s="2"/>
-    </row>
-    <row r="34" ht="18" customHeight="1" spans="1:13">
+      <c r="O33" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1" spans="1:15">
       <c r="A34" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>78</v>
@@ -9311,16 +9674,16 @@
         <v>79</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="4"/>
@@ -9328,10 +9691,13 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
       <c r="M34" s="2"/>
-    </row>
-    <row r="35" ht="18" customHeight="1" spans="1:13">
+      <c r="O34" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1" spans="1:15">
       <c r="A35" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>78</v>
@@ -9340,16 +9706,16 @@
         <v>79</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="4"/>
@@ -9357,10 +9723,13 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
       <c r="M35" s="2"/>
-    </row>
-    <row r="36" ht="18" customHeight="1" spans="1:13">
+      <c r="O35" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" ht="18" customHeight="1" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>78</v>
@@ -9369,16 +9738,16 @@
         <v>79</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="4"/>
@@ -9386,6 +9755,9 @@
       <c r="K36" s="3"/>
       <c r="L36" s="3"/>
       <c r="M36" s="2"/>
+      <c r="O36" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="37" spans="9:9">
       <c r="I37" s="4"/>
